--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484218_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484218_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>4.0369</v>
+        <v>3.7142</v>
       </c>
       <c r="E2" t="n">
-        <v>4.3458</v>
+        <v>3.9414</v>
       </c>
       <c r="F2" t="n">
-        <v>-0.3089</v>
+        <v>-0.2272</v>
       </c>
       <c r="G2" t="n">
         <v>2.7691</v>
@@ -610,13 +610,13 @@
         <v>1.5627</v>
       </c>
       <c r="S2" t="n">
-        <v>0.6818</v>
+        <v>0.3591</v>
       </c>
       <c r="T2" t="n">
-        <v>1.2355</v>
+        <v>0.831</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.5537</v>
+        <v>-0.472</v>
       </c>
       <c r="V2" t="n">
         <v>0</v>
@@ -631,7 +631,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>A. CANO CANO</t>
+          <t>M. SERRAT PONCE</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,73 +643,73 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>1.9118</v>
+        <v>1.4528</v>
       </c>
       <c r="E3" t="n">
-        <v>3.81</v>
+        <v>0.2997</v>
       </c>
       <c r="F3" t="n">
-        <v>-1.8982</v>
+        <v>1.1531</v>
       </c>
       <c r="G3" t="n">
-        <v>0.7079</v>
+        <v>-0.4063</v>
       </c>
       <c r="H3" t="n">
-        <v>-1.2617</v>
+        <v>-1.5794</v>
       </c>
       <c r="I3" t="n">
-        <v>1.9696</v>
+        <v>1.1731</v>
       </c>
       <c r="J3" t="n">
-        <v>3.3093</v>
+        <v>0.1076</v>
       </c>
       <c r="K3" t="n">
-        <v>0.7994</v>
+        <v>0.1471</v>
       </c>
       <c r="L3" t="n">
-        <v>2.5099</v>
+        <v>-0.0395</v>
       </c>
       <c r="M3" t="n">
-        <v>-2.6014</v>
+        <v>-0.5139</v>
       </c>
       <c r="N3" t="n">
-        <v>-2.0611</v>
+        <v>-1.7265</v>
       </c>
       <c r="O3" t="n">
-        <v>-0.5403</v>
+        <v>1.2126</v>
       </c>
       <c r="P3" t="n">
-        <v>0.586</v>
+        <v>2.3441</v>
       </c>
       <c r="Q3" t="n">
-        <v>-0.9767</v>
+        <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>1.5627</v>
+        <v>2.3441</v>
       </c>
       <c r="S3" t="n">
-        <v>0.8401999999999999</v>
+        <v>0.06950000000000001</v>
       </c>
       <c r="T3" t="n">
-        <v>0.2588</v>
+        <v>0.1921</v>
       </c>
       <c r="U3" t="n">
-        <v>0.5814</v>
+        <v>-0.1226</v>
       </c>
       <c r="V3" t="n">
-        <v>-0.2224</v>
+        <v>-0.5545</v>
       </c>
       <c r="W3" t="n">
-        <v>1.2186</v>
+        <v>0</v>
       </c>
       <c r="X3" t="n">
-        <v>-1.441</v>
+        <v>-0.5545</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>M. SERRAT PONCE</t>
+          <t>A. CANO CANO</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,67 +721,67 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>0.3521</v>
+        <v>0.9704</v>
       </c>
       <c r="E4" t="n">
-        <v>-0.6103</v>
+        <v>3.3044</v>
       </c>
       <c r="F4" t="n">
-        <v>0.9625</v>
+        <v>-2.334</v>
       </c>
       <c r="G4" t="n">
-        <v>-0.4063</v>
+        <v>0.7079</v>
       </c>
       <c r="H4" t="n">
-        <v>-1.5794</v>
+        <v>-1.2617</v>
       </c>
       <c r="I4" t="n">
-        <v>1.1731</v>
+        <v>1.9696</v>
       </c>
       <c r="J4" t="n">
-        <v>0.1076</v>
+        <v>3.3093</v>
       </c>
       <c r="K4" t="n">
-        <v>0.1471</v>
+        <v>0.7994</v>
       </c>
       <c r="L4" t="n">
-        <v>-0.0395</v>
+        <v>2.5099</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.5139</v>
+        <v>-2.6014</v>
       </c>
       <c r="N4" t="n">
-        <v>-1.7265</v>
+        <v>-2.0611</v>
       </c>
       <c r="O4" t="n">
-        <v>1.2126</v>
+        <v>-0.5403</v>
       </c>
       <c r="P4" t="n">
-        <v>2.3441</v>
+        <v>0.586</v>
       </c>
       <c r="Q4" t="n">
-        <v>0</v>
+        <v>-0.9767</v>
       </c>
       <c r="R4" t="n">
-        <v>2.3441</v>
+        <v>1.5627</v>
       </c>
       <c r="S4" t="n">
-        <v>-1.0312</v>
+        <v>-0.1011</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.7179</v>
+        <v>-0.2468</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.3133</v>
+        <v>0.1457</v>
       </c>
       <c r="V4" t="n">
-        <v>-0.5545</v>
+        <v>-0.2224</v>
       </c>
       <c r="W4" t="n">
-        <v>0</v>
+        <v>1.2186</v>
       </c>
       <c r="X4" t="n">
-        <v>-0.5545</v>
+        <v>-1.441</v>
       </c>
     </row>
     <row r="5">
@@ -799,10 +799,10 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.2504</v>
+        <v>-0.9582000000000001</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.1006</v>
+        <v>-0.8084</v>
       </c>
       <c r="F5" t="n">
         <v>-0.1498</v>
@@ -844,10 +844,10 @@
         <v>0</v>
       </c>
       <c r="S5" t="n">
-        <v>1.0923</v>
+        <v>0.3845</v>
       </c>
       <c r="T5" t="n">
-        <v>1.2272</v>
+        <v>0.5193</v>
       </c>
       <c r="U5" t="n">
         <v>-0.1348</v>
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-1.57</v>
+        <v>-1.0137</v>
       </c>
       <c r="E6" t="n">
-        <v>-1.5324</v>
+        <v>-1.3302</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.0375</v>
+        <v>0.3165</v>
       </c>
       <c r="G6" t="n">
         <v>-3.0563</v>
@@ -922,13 +922,13 @@
         <v>0.9767</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.3416</v>
+        <v>0.2146</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.1732</v>
+        <v>0.029</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.1684</v>
+        <v>0.1856</v>
       </c>
       <c r="V6" t="n">
         <v>1.8279</v>
@@ -943,7 +943,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>J. SALAVEDRA VILARNAU</t>
+          <t>M. MONTSERRAT SERRA</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,64 +955,64 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-1.5879</v>
+        <v>-2.1853</v>
       </c>
       <c r="E7" t="n">
-        <v>-1.216</v>
+        <v>-0.5928</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.3719</v>
+        <v>-1.5925</v>
       </c>
       <c r="G7" t="n">
-        <v>-2.6042</v>
+        <v>-1.0713</v>
       </c>
       <c r="H7" t="n">
-        <v>-1.8755</v>
+        <v>-0.8956</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.7288</v>
+        <v>-0.1757</v>
       </c>
       <c r="J7" t="n">
-        <v>-0.8963</v>
+        <v>1.1807</v>
       </c>
       <c r="K7" t="n">
-        <v>-0.9772999999999999</v>
+        <v>0.4119</v>
       </c>
       <c r="L7" t="n">
-        <v>0.0809</v>
+        <v>0.7688</v>
       </c>
       <c r="M7" t="n">
-        <v>-1.7079</v>
+        <v>-2.252</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.8982</v>
+        <v>-1.3075</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.8097</v>
+        <v>-0.9445</v>
       </c>
       <c r="P7" t="n">
-        <v>-0.1953</v>
+        <v>0.1953</v>
       </c>
       <c r="Q7" t="n">
         <v>-0.9767</v>
       </c>
       <c r="R7" t="n">
-        <v>0.7814</v>
+        <v>1.1721</v>
       </c>
       <c r="S7" t="n">
-        <v>1.2117</v>
+        <v>-0.3679</v>
       </c>
       <c r="T7" t="n">
-        <v>0.3798</v>
+        <v>-0.1326</v>
       </c>
       <c r="U7" t="n">
-        <v>0.8319</v>
+        <v>-0.2353</v>
       </c>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>-0.9414</v>
       </c>
       <c r="W7" t="n">
-        <v>0.2772</v>
+        <v>-0.6642</v>
       </c>
       <c r="X7" t="n">
         <v>-0.2772</v>
@@ -1021,7 +1021,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>M. MONTSERRAT SERRA</t>
+          <t>J. SALAVEDRA VILARNAU</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,64 +1033,64 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-2.3681</v>
+        <v>-2.2569</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.6939</v>
+        <v>-1.7216</v>
       </c>
       <c r="F8" t="n">
-        <v>-1.6742</v>
+        <v>-0.5353</v>
       </c>
       <c r="G8" t="n">
-        <v>-1.0713</v>
+        <v>-2.6042</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.8956</v>
+        <v>-1.8755</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.1757</v>
+        <v>-0.7288</v>
       </c>
       <c r="J8" t="n">
-        <v>1.1807</v>
+        <v>-0.8963</v>
       </c>
       <c r="K8" t="n">
-        <v>0.4119</v>
+        <v>-0.9772999999999999</v>
       </c>
       <c r="L8" t="n">
-        <v>0.7688</v>
+        <v>0.0809</v>
       </c>
       <c r="M8" t="n">
-        <v>-2.252</v>
+        <v>-1.7079</v>
       </c>
       <c r="N8" t="n">
-        <v>-1.3075</v>
+        <v>-0.8982</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.9445</v>
+        <v>-0.8097</v>
       </c>
       <c r="P8" t="n">
-        <v>0.1953</v>
+        <v>-0.1953</v>
       </c>
       <c r="Q8" t="n">
         <v>-0.9767</v>
       </c>
       <c r="R8" t="n">
-        <v>1.1721</v>
+        <v>0.7814</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.5508</v>
+        <v>0.5427</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.2337</v>
+        <v>-0.1257</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.317</v>
+        <v>0.6685</v>
       </c>
       <c r="V8" t="n">
-        <v>-0.9414</v>
+        <v>0</v>
       </c>
       <c r="W8" t="n">
-        <v>-0.6642</v>
+        <v>0.2772</v>
       </c>
       <c r="X8" t="n">
         <v>-0.2772</v>
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-3.1591</v>
+        <v>-2.2722</v>
       </c>
       <c r="E9" t="n">
-        <v>-3.3887</v>
+        <v>-2.8832</v>
       </c>
       <c r="F9" t="n">
-        <v>0.2297</v>
+        <v>0.611</v>
       </c>
       <c r="G9" t="n">
         <v>-2.4724</v>
@@ -1156,13 +1156,13 @@
         <v>2.3441</v>
       </c>
       <c r="S9" t="n">
-        <v>-1.0773</v>
+        <v>-0.1904</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.2859</v>
+        <v>0.2197</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.7914</v>
+        <v>-0.4101</v>
       </c>
       <c r="V9" t="n">
         <v>0</v>
@@ -1177,7 +1177,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>M. MATEU SERRA</t>
+          <t>M. CAPELL OLLER</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,73 +1189,73 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-3.4335</v>
+        <v>-3.5837</v>
       </c>
       <c r="E10" t="n">
-        <v>-3.8584</v>
+        <v>-2.5045</v>
       </c>
       <c r="F10" t="n">
-        <v>0.4249</v>
+        <v>-1.0792</v>
       </c>
       <c r="G10" t="n">
-        <v>-2.3482</v>
+        <v>-2.0428</v>
       </c>
       <c r="H10" t="n">
-        <v>-1.7949</v>
+        <v>-1.1796</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.5533</v>
+        <v>-0.8632</v>
       </c>
       <c r="J10" t="n">
-        <v>-0.8354</v>
+        <v>-0.1301</v>
       </c>
       <c r="K10" t="n">
-        <v>-0.2827</v>
+        <v>-0.07679999999999999</v>
       </c>
       <c r="L10" t="n">
-        <v>-0.5527</v>
+        <v>-0.0533</v>
       </c>
       <c r="M10" t="n">
-        <v>-1.5127</v>
+        <v>-1.9127</v>
       </c>
       <c r="N10" t="n">
-        <v>-1.5121</v>
+        <v>-1.1028</v>
       </c>
       <c r="O10" t="n">
-        <v>-0.0005999999999999999</v>
+        <v>-0.8099</v>
       </c>
       <c r="P10" t="n">
-        <v>-0.586</v>
+        <v>-3.3208</v>
       </c>
       <c r="Q10" t="n">
-        <v>-1.9534</v>
+        <v>-3.9069</v>
       </c>
       <c r="R10" t="n">
-        <v>1.3674</v>
+        <v>0.586</v>
       </c>
       <c r="S10" t="n">
-        <v>1.4384</v>
+        <v>0.0069</v>
       </c>
       <c r="T10" t="n">
-        <v>0.2588</v>
+        <v>-0.2406</v>
       </c>
       <c r="U10" t="n">
-        <v>1.1796</v>
+        <v>0.2475</v>
       </c>
       <c r="V10" t="n">
-        <v>-1.9376</v>
+        <v>1.7731</v>
       </c>
       <c r="W10" t="n">
-        <v>-1.3283</v>
+        <v>1.7731</v>
       </c>
       <c r="X10" t="n">
-        <v>-0.6093</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>M. CAPELL OLLER</t>
+          <t>M. MATEU SERRA</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,67 +1267,67 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-4.2993</v>
+        <v>-4.2349</v>
       </c>
       <c r="E11" t="n">
-        <v>-3.1112</v>
+        <v>-4.0606</v>
       </c>
       <c r="F11" t="n">
-        <v>-1.1881</v>
+        <v>-0.1743</v>
       </c>
       <c r="G11" t="n">
-        <v>-2.0428</v>
+        <v>-2.3482</v>
       </c>
       <c r="H11" t="n">
-        <v>-1.1796</v>
+        <v>-1.7949</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.8632</v>
+        <v>-0.5533</v>
       </c>
       <c r="J11" t="n">
-        <v>-0.1301</v>
+        <v>-0.8354</v>
       </c>
       <c r="K11" t="n">
-        <v>-0.07679999999999999</v>
+        <v>-0.2827</v>
       </c>
       <c r="L11" t="n">
-        <v>-0.0533</v>
+        <v>-0.5527</v>
       </c>
       <c r="M11" t="n">
-        <v>-1.9127</v>
+        <v>-1.5127</v>
       </c>
       <c r="N11" t="n">
-        <v>-1.1028</v>
+        <v>-1.5121</v>
       </c>
       <c r="O11" t="n">
-        <v>-0.8099</v>
+        <v>-0.0005999999999999999</v>
       </c>
       <c r="P11" t="n">
-        <v>-3.3208</v>
+        <v>-0.586</v>
       </c>
       <c r="Q11" t="n">
-        <v>-3.9069</v>
+        <v>-1.9534</v>
       </c>
       <c r="R11" t="n">
-        <v>0.586</v>
+        <v>1.3674</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.7087</v>
+        <v>0.637</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.8473000000000001</v>
+        <v>0.0566</v>
       </c>
       <c r="U11" t="n">
-        <v>0.1386</v>
+        <v>0.5804</v>
       </c>
       <c r="V11" t="n">
-        <v>1.7731</v>
+        <v>-1.9376</v>
       </c>
       <c r="W11" t="n">
-        <v>1.7731</v>
+        <v>-1.3283</v>
       </c>
       <c r="X11" t="n">
-        <v>0</v>
+        <v>-0.6093</v>
       </c>
     </row>
     <row r="12">
@@ -1348,10 +1348,10 @@
         <v>-10.3675</v>
       </c>
       <c r="E12" t="n">
-        <v>-6.355700000000001</v>
+        <v>-6.355800000000001</v>
       </c>
       <c r="F12" t="n">
-        <v>-4.0115</v>
+        <v>-4.011699999999999</v>
       </c>
       <c r="G12" t="n">
         <v>-12.5314</v>
@@ -1366,10 +1366,10 @@
         <v>1.248699999999999</v>
       </c>
       <c r="K12" t="n">
-        <v>-2.8027</v>
+        <v>-2.802700000000001</v>
       </c>
       <c r="L12" t="n">
-        <v>4.051500000000001</v>
+        <v>4.0515</v>
       </c>
       <c r="M12" t="n">
         <v>-13.7801</v>
@@ -1378,10 +1378,10 @@
         <v>-14.4473</v>
       </c>
       <c r="O12" t="n">
-        <v>0.6670999999999999</v>
+        <v>0.6671</v>
       </c>
       <c r="P12" t="n">
-        <v>-4.440892098500626e-16</v>
+        <v>-5.551115123125783e-16</v>
       </c>
       <c r="Q12" t="n">
         <v>-12.6972</v>
@@ -1390,19 +1390,19 @@
         <v>12.6972</v>
       </c>
       <c r="S12" t="n">
-        <v>1.5548</v>
+        <v>1.5549</v>
       </c>
       <c r="T12" t="n">
-        <v>1.1021</v>
+        <v>1.102</v>
       </c>
       <c r="U12" t="n">
-        <v>0.4528999999999999</v>
+        <v>0.4529</v>
       </c>
       <c r="V12" t="n">
         <v>0.6093</v>
       </c>
       <c r="W12" t="n">
-        <v>3.990899999999999</v>
+        <v>3.9909</v>
       </c>
       <c r="X12" t="n">
         <v>-3.3815</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>12.5688</v>
+        <v>10.0484</v>
       </c>
       <c r="E13" t="n">
-        <v>10.5024</v>
+        <v>8.581200000000001</v>
       </c>
       <c r="F13" t="n">
-        <v>2.0664</v>
+        <v>1.4672</v>
       </c>
       <c r="G13" t="n">
         <v>7.8526</v>
@@ -1468,13 +1468,13 @@
         <v>2.3441</v>
       </c>
       <c r="S13" t="n">
-        <v>3.1497</v>
+        <v>0.6293</v>
       </c>
       <c r="T13" t="n">
-        <v>2.7131</v>
+        <v>0.7919</v>
       </c>
       <c r="U13" t="n">
-        <v>0.4366</v>
+        <v>-0.1626</v>
       </c>
       <c r="V13" t="n">
         <v>-0.3869</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>2.4746</v>
+        <v>2.8869</v>
       </c>
       <c r="E15" t="n">
-        <v>2.3084</v>
+        <v>2.6118</v>
       </c>
       <c r="F15" t="n">
-        <v>0.1662</v>
+        <v>0.2751</v>
       </c>
       <c r="G15" t="n">
         <v>2.3044</v>
@@ -1624,13 +1624,13 @@
         <v>1.5627</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.8381</v>
+        <v>-0.4259</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.9078000000000001</v>
+        <v>-0.6045</v>
       </c>
       <c r="U15" t="n">
-        <v>0.0697</v>
+        <v>0.1786</v>
       </c>
       <c r="V15" t="n">
         <v>-0.5545</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>0.4559</v>
+        <v>1.0238</v>
       </c>
       <c r="E16" t="n">
-        <v>1.5131</v>
+        <v>1.9175</v>
       </c>
       <c r="F16" t="n">
-        <v>-1.0572</v>
+        <v>-0.8938</v>
       </c>
       <c r="G16" t="n">
         <v>0.289</v>
@@ -1702,13 +1702,13 @@
         <v>0.586</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.5514</v>
+        <v>0.0165</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.4237</v>
+        <v>-0.0192</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.1277</v>
+        <v>0.0357</v>
       </c>
       <c r="V16" t="n">
         <v>1.1089</v>
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>0.1381</v>
+        <v>0.5075</v>
       </c>
       <c r="E17" t="n">
-        <v>-1.4447</v>
+        <v>-0.9391</v>
       </c>
       <c r="F17" t="n">
-        <v>1.5828</v>
+        <v>1.4466</v>
       </c>
       <c r="G17" t="n">
         <v>0.2726</v>
@@ -1780,13 +1780,13 @@
         <v>0.9767</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.6852</v>
+        <v>-0.3158</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.7262999999999999</v>
+        <v>-0.2207</v>
       </c>
       <c r="U17" t="n">
-        <v>0.0411</v>
+        <v>-0.0951</v>
       </c>
       <c r="V17" t="n">
         <v>0.9414</v>
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>0.0481</v>
+        <v>0.4059</v>
       </c>
       <c r="E18" t="n">
-        <v>-1.2056</v>
+        <v>-0.9022</v>
       </c>
       <c r="F18" t="n">
-        <v>1.2537</v>
+        <v>1.3082</v>
       </c>
       <c r="G18" t="n">
         <v>-0.8339</v>
@@ -1858,13 +1858,13 @@
         <v>0.7814</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.1728</v>
+        <v>0.185</v>
       </c>
       <c r="T18" t="n">
-        <v>0.1294</v>
+        <v>0.4327</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.3022</v>
+        <v>-0.2477</v>
       </c>
       <c r="V18" t="n">
         <v>0.6642</v>
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.8763</v>
+        <v>-0.8218</v>
       </c>
       <c r="E19" t="n">
         <v>-0.9562</v>
       </c>
       <c r="F19" t="n">
-        <v>0.0799</v>
+        <v>0.1344</v>
       </c>
       <c r="G19" t="n">
         <v>-0.4538</v>
@@ -1936,13 +1936,13 @@
         <v>0.3907</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.5359</v>
+        <v>-0.4815</v>
       </c>
       <c r="T19" t="n">
         <v>-0.3026</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.2333</v>
+        <v>-0.1789</v>
       </c>
       <c r="V19" t="n">
         <v>-0.2772</v>
@@ -1957,7 +1957,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>M. SEGARRA BAQUES</t>
+          <t>D. ROY CARNICER</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,73 +1969,73 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-2.2377</v>
+        <v>-2.3152</v>
       </c>
       <c r="E20" t="n">
-        <v>-3.1768</v>
+        <v>-1.8994</v>
       </c>
       <c r="F20" t="n">
-        <v>0.9391</v>
+        <v>-0.4158</v>
       </c>
       <c r="G20" t="n">
-        <v>0.5531</v>
+        <v>-1.0828</v>
       </c>
       <c r="H20" t="n">
-        <v>0.4718</v>
+        <v>0.8726</v>
       </c>
       <c r="I20" t="n">
-        <v>0.0813</v>
+        <v>-1.9554</v>
       </c>
       <c r="J20" t="n">
-        <v>-0.2963</v>
+        <v>-0.3182</v>
       </c>
       <c r="K20" t="n">
-        <v>0.431</v>
+        <v>0.2878</v>
       </c>
       <c r="L20" t="n">
-        <v>-0.7274</v>
+        <v>-0.606</v>
       </c>
       <c r="M20" t="n">
-        <v>0.8494</v>
+        <v>-0.7645</v>
       </c>
       <c r="N20" t="n">
-        <v>0.0407</v>
+        <v>0.5848</v>
       </c>
       <c r="O20" t="n">
-        <v>0.8087</v>
+        <v>-1.3494</v>
       </c>
       <c r="P20" t="n">
-        <v>-2.1488</v>
+        <v>0.7814</v>
       </c>
       <c r="Q20" t="n">
-        <v>-3.3208</v>
+        <v>-0.9767</v>
       </c>
       <c r="R20" t="n">
-        <v>1.1721</v>
+        <v>1.7581</v>
       </c>
       <c r="S20" t="n">
-        <v>0.5766</v>
+        <v>-0.518</v>
       </c>
       <c r="T20" t="n">
-        <v>0.4404</v>
+        <v>-0.6045</v>
       </c>
       <c r="U20" t="n">
-        <v>0.1363</v>
+        <v>0.08649999999999999</v>
       </c>
       <c r="V20" t="n">
-        <v>-1.2186</v>
+        <v>-1.4959</v>
       </c>
       <c r="W20" t="n">
         <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>-1.2186</v>
+        <v>-1.4959</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>D. ROY CARNICER</t>
+          <t>J. MARTIN TRENADO</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,73 +2047,73 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-2.5913</v>
+        <v>-2.6666</v>
       </c>
       <c r="E21" t="n">
-        <v>-2.2028</v>
+        <v>-2.9414</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.3886</v>
+        <v>0.2748</v>
       </c>
       <c r="G21" t="n">
-        <v>-1.0828</v>
+        <v>-0.1855</v>
       </c>
       <c r="H21" t="n">
-        <v>0.8726</v>
+        <v>4.4398</v>
       </c>
       <c r="I21" t="n">
-        <v>-1.9554</v>
+        <v>-4.6253</v>
       </c>
       <c r="J21" t="n">
-        <v>-0.3182</v>
+        <v>0.2494</v>
       </c>
       <c r="K21" t="n">
-        <v>0.2878</v>
+        <v>3.5252</v>
       </c>
       <c r="L21" t="n">
-        <v>-0.606</v>
+        <v>-3.2757</v>
       </c>
       <c r="M21" t="n">
-        <v>-0.7645</v>
+        <v>-0.435</v>
       </c>
       <c r="N21" t="n">
-        <v>0.5848</v>
+        <v>0.9146</v>
       </c>
       <c r="O21" t="n">
-        <v>-1.3494</v>
+        <v>-1.3496</v>
       </c>
       <c r="P21" t="n">
-        <v>0.7814</v>
+        <v>-2.5395</v>
       </c>
       <c r="Q21" t="n">
-        <v>-0.9767</v>
+        <v>-4.2975</v>
       </c>
       <c r="R21" t="n">
         <v>1.7581</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.7941</v>
+        <v>-0.551</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.9078000000000001</v>
+        <v>-0.112</v>
       </c>
       <c r="U21" t="n">
-        <v>0.1137</v>
+        <v>-0.439</v>
       </c>
       <c r="V21" t="n">
-        <v>-1.4959</v>
+        <v>0.6093</v>
       </c>
       <c r="W21" t="n">
-        <v>0</v>
+        <v>1.2186</v>
       </c>
       <c r="X21" t="n">
-        <v>-1.4959</v>
+        <v>-0.6093</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>J. MARTIN TRENADO</t>
+          <t>M. SEGARRA BAQUES</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,67 +2125,67 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-3.5964</v>
+        <v>-2.685</v>
       </c>
       <c r="E22" t="n">
-        <v>-3.2448</v>
+        <v>-3.379</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.3516</v>
+        <v>0.694</v>
       </c>
       <c r="G22" t="n">
-        <v>-0.1855</v>
+        <v>0.5531</v>
       </c>
       <c r="H22" t="n">
-        <v>4.4398</v>
+        <v>0.4718</v>
       </c>
       <c r="I22" t="n">
-        <v>-4.6253</v>
+        <v>0.0813</v>
       </c>
       <c r="J22" t="n">
-        <v>0.2494</v>
+        <v>-0.2963</v>
       </c>
       <c r="K22" t="n">
-        <v>3.5252</v>
+        <v>0.431</v>
       </c>
       <c r="L22" t="n">
-        <v>-3.2757</v>
+        <v>-0.7274</v>
       </c>
       <c r="M22" t="n">
-        <v>-0.435</v>
+        <v>0.8494</v>
       </c>
       <c r="N22" t="n">
-        <v>0.9146</v>
+        <v>0.0407</v>
       </c>
       <c r="O22" t="n">
-        <v>-1.3496</v>
+        <v>0.8087</v>
       </c>
       <c r="P22" t="n">
-        <v>-2.5395</v>
+        <v>-2.1488</v>
       </c>
       <c r="Q22" t="n">
-        <v>-4.2975</v>
+        <v>-3.3208</v>
       </c>
       <c r="R22" t="n">
-        <v>1.7581</v>
+        <v>1.1721</v>
       </c>
       <c r="S22" t="n">
-        <v>-1.4807</v>
+        <v>0.1293</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.4153</v>
+        <v>0.2381</v>
       </c>
       <c r="U22" t="n">
-        <v>-1.0654</v>
+        <v>-0.1088</v>
       </c>
       <c r="V22" t="n">
-        <v>0.6093</v>
+        <v>-1.2186</v>
       </c>
       <c r="W22" t="n">
-        <v>1.2186</v>
+        <v>0</v>
       </c>
       <c r="X22" t="n">
-        <v>-0.6093</v>
+        <v>-1.2186</v>
       </c>
     </row>
     <row r="23">
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>10.3674</v>
+        <v>10.3675</v>
       </c>
       <c r="E23" t="n">
-        <v>4.011699999999999</v>
+        <v>4.011900000000001</v>
       </c>
       <c r="F23" t="n">
-        <v>6.355599999999999</v>
+        <v>6.355600000000001</v>
       </c>
       <c r="G23" t="n">
         <v>12.5315</v>
@@ -2227,7 +2227,7 @@
         <v>14.4474</v>
       </c>
       <c r="L23" t="n">
-        <v>-0.6671999999999998</v>
+        <v>-0.6671999999999996</v>
       </c>
       <c r="M23" t="n">
         <v>-1.2487</v>
@@ -2239,7 +2239,7 @@
         <v>-4.0515</v>
       </c>
       <c r="P23" t="n">
-        <v>-0.000100000000000211</v>
+        <v>-9.999999999976694e-05</v>
       </c>
       <c r="Q23" t="n">
         <v>-12.6972</v>
@@ -2248,16 +2248,16 @@
         <v>12.6973</v>
       </c>
       <c r="S23" t="n">
-        <v>-1.5548</v>
+        <v>-1.555</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.4528000000000003</v>
+        <v>-0.4530000000000001</v>
       </c>
       <c r="U23" t="n">
-        <v>-1.1019</v>
+        <v>-1.102</v>
       </c>
       <c r="V23" t="n">
-        <v>-0.6093000000000002</v>
+        <v>-0.6093</v>
       </c>
       <c r="W23" t="n">
         <v>3.3816</v>

--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484218_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484218_PROCESSED_CHRONO.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X23"/>
+  <dimension ref="A1:Y25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -549,6 +549,11 @@
           <t>Def_FT</t>
         </is>
       </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>Game_File</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -627,6 +632,11 @@
       <c r="X2" t="n">
         <v>-1.2186</v>
       </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>play_by_play_2484218_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -705,6 +715,11 @@
       <c r="X3" t="n">
         <v>-0.5545</v>
       </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>play_by_play_2484218_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -783,6 +798,11 @@
       <c r="X4" t="n">
         <v>-1.441</v>
       </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>play_by_play_2484218_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -861,6 +881,11 @@
       <c r="X5" t="n">
         <v>0.6642</v>
       </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>play_by_play_2484218_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -939,6 +964,11 @@
       <c r="X6" t="n">
         <v>0.3321</v>
       </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>play_by_play_2484218_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1017,6 +1047,11 @@
       <c r="X7" t="n">
         <v>-0.2772</v>
       </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>play_by_play_2484218_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1095,6 +1130,11 @@
       <c r="X8" t="n">
         <v>-0.2772</v>
       </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>play_by_play_2484218_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1173,6 +1213,11 @@
       <c r="X9" t="n">
         <v>0</v>
       </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>play_by_play_2484218_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1251,6 +1296,11 @@
       <c r="X10" t="n">
         <v>0</v>
       </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>play_by_play_2484218_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1329,6 +1379,11 @@
       <c r="X11" t="n">
         <v>-0.6093</v>
       </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>play_by_play_2484218_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1407,6 +1462,7 @@
       <c r="X12" t="n">
         <v>-3.3815</v>
       </c>
+      <c r="Y12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1485,6 +1541,11 @@
       <c r="X13" t="n">
         <v>0</v>
       </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>play_by_play_2484218_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1563,6 +1624,11 @@
       <c r="X14" t="n">
         <v>0</v>
       </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>play_by_play_2484218_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1641,6 +1707,11 @@
       <c r="X15" t="n">
         <v>-0.8317</v>
       </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>play_by_play_2484218_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1719,11 +1790,16 @@
       <c r="X16" t="n">
         <v>-0.8865</v>
       </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>play_by_play_2484218_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Q. BARDÉS BADIA</t>
+          <t>P. CAMPAÑA SOLER</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1811,78 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>0.5075</v>
+        <v>0.607</v>
       </c>
       <c r="E17" t="n">
-        <v>-0.9391</v>
+        <v>0.607</v>
       </c>
       <c r="F17" t="n">
-        <v>1.4466</v>
+        <v>0</v>
       </c>
       <c r="G17" t="n">
-        <v>0.2726</v>
+        <v>0.607</v>
       </c>
       <c r="H17" t="n">
-        <v>1.0412</v>
+        <v>0</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.7687</v>
+        <v>0.607</v>
       </c>
       <c r="J17" t="n">
-        <v>0.3717</v>
+        <v>0.607</v>
       </c>
       <c r="K17" t="n">
-        <v>1.6795</v>
+        <v>0</v>
       </c>
       <c r="L17" t="n">
-        <v>-1.3077</v>
+        <v>0.607</v>
       </c>
       <c r="M17" t="n">
-        <v>-0.0992</v>
+        <v>0</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.6382</v>
+        <v>0</v>
       </c>
       <c r="O17" t="n">
-        <v>0.5391</v>
+        <v>0</v>
       </c>
       <c r="P17" t="n">
-        <v>-0.3907</v>
+        <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>-1.3674</v>
+        <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>0.9767</v>
+        <v>0</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.3158</v>
+        <v>0</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.2207</v>
+        <v>0</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.0951</v>
+        <v>0</v>
       </c>
       <c r="V17" t="n">
-        <v>0.9414</v>
+        <v>0</v>
       </c>
       <c r="W17" t="n">
-        <v>0.2772</v>
+        <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>0.6642</v>
+        <v>0</v>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>play_by_play_2484218_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>P. CAMPAÑA SOLER</t>
+          <t>Q. BARDÉS BADIA</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1894,78 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>0.4059</v>
+        <v>0.307</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.9022</v>
+        <v>0.307</v>
       </c>
       <c r="F18" t="n">
-        <v>1.3082</v>
+        <v>0</v>
       </c>
       <c r="G18" t="n">
-        <v>-0.8339</v>
+        <v>0.307</v>
       </c>
       <c r="H18" t="n">
-        <v>-0.5779</v>
+        <v>0.307</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.256</v>
+        <v>0</v>
       </c>
       <c r="J18" t="n">
-        <v>-0.9443</v>
+        <v>0.307</v>
       </c>
       <c r="K18" t="n">
-        <v>-0.284</v>
+        <v>0.307</v>
       </c>
       <c r="L18" t="n">
-        <v>-0.6603</v>
+        <v>0</v>
       </c>
       <c r="M18" t="n">
-        <v>0.1103</v>
+        <v>0</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.2939</v>
+        <v>0</v>
       </c>
       <c r="O18" t="n">
-        <v>0.4043</v>
+        <v>0</v>
       </c>
       <c r="P18" t="n">
-        <v>0.3907</v>
+        <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>-0.3907</v>
+        <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>0.7814</v>
+        <v>0</v>
       </c>
       <c r="S18" t="n">
-        <v>0.185</v>
+        <v>0</v>
       </c>
       <c r="T18" t="n">
-        <v>0.4327</v>
+        <v>0</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.2477</v>
+        <v>0</v>
       </c>
       <c r="V18" t="n">
-        <v>0.6642</v>
+        <v>0</v>
       </c>
       <c r="W18" t="n">
         <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>0.6642</v>
+        <v>0</v>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>play_by_play_2484218_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>S. ROMEO FO</t>
+          <t>Q. BARDES BADIA</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1977,78 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.8218</v>
+        <v>0.2005</v>
       </c>
       <c r="E19" t="n">
-        <v>-0.9562</v>
+        <v>-1.2461</v>
       </c>
       <c r="F19" t="n">
-        <v>0.1344</v>
+        <v>1.4466</v>
       </c>
       <c r="G19" t="n">
-        <v>-0.4538</v>
+        <v>-0.0344</v>
       </c>
       <c r="H19" t="n">
-        <v>-0.5887</v>
+        <v>0.7342</v>
       </c>
       <c r="I19" t="n">
-        <v>0.1348</v>
+        <v>-0.7687</v>
       </c>
       <c r="J19" t="n">
-        <v>-0.6536</v>
+        <v>0.06469999999999999</v>
       </c>
       <c r="K19" t="n">
-        <v>-0.6536</v>
+        <v>1.3725</v>
       </c>
       <c r="L19" t="n">
-        <v>0</v>
+        <v>-1.3077</v>
       </c>
       <c r="M19" t="n">
-        <v>0.1998</v>
+        <v>-0.0992</v>
       </c>
       <c r="N19" t="n">
-        <v>0.065</v>
+        <v>-0.6382</v>
       </c>
       <c r="O19" t="n">
-        <v>0.1348</v>
+        <v>0.5391</v>
       </c>
       <c r="P19" t="n">
-        <v>0.3907</v>
+        <v>-0.3907</v>
       </c>
       <c r="Q19" t="n">
-        <v>0</v>
+        <v>-1.3674</v>
       </c>
       <c r="R19" t="n">
-        <v>0.3907</v>
+        <v>0.9767</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.4815</v>
+        <v>-0.3158</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.3026</v>
+        <v>-0.2207</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.1789</v>
+        <v>-0.0951</v>
       </c>
       <c r="V19" t="n">
-        <v>-0.2772</v>
+        <v>0.9414</v>
       </c>
       <c r="W19" t="n">
-        <v>0</v>
+        <v>0.2772</v>
       </c>
       <c r="X19" t="n">
-        <v>-0.2772</v>
+        <v>0.6642</v>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>play_by_play_2484218_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>D. ROY CARNICER</t>
+          <t>P. CAMPANA SOLER</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,73 +2060,78 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-2.3152</v>
+        <v>-0.201</v>
       </c>
       <c r="E20" t="n">
-        <v>-1.8994</v>
+        <v>-1.5092</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.4158</v>
+        <v>1.3082</v>
       </c>
       <c r="G20" t="n">
-        <v>-1.0828</v>
+        <v>-1.4409</v>
       </c>
       <c r="H20" t="n">
-        <v>0.8726</v>
+        <v>-0.5779</v>
       </c>
       <c r="I20" t="n">
-        <v>-1.9554</v>
+        <v>-0.863</v>
       </c>
       <c r="J20" t="n">
-        <v>-0.3182</v>
+        <v>-1.5512</v>
       </c>
       <c r="K20" t="n">
-        <v>0.2878</v>
+        <v>-0.284</v>
       </c>
       <c r="L20" t="n">
-        <v>-0.606</v>
+        <v>-1.2673</v>
       </c>
       <c r="M20" t="n">
-        <v>-0.7645</v>
+        <v>0.1103</v>
       </c>
       <c r="N20" t="n">
-        <v>0.5848</v>
+        <v>-0.2939</v>
       </c>
       <c r="O20" t="n">
-        <v>-1.3494</v>
+        <v>0.4043</v>
       </c>
       <c r="P20" t="n">
+        <v>0.3907</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>-0.3907</v>
+      </c>
+      <c r="R20" t="n">
         <v>0.7814</v>
       </c>
-      <c r="Q20" t="n">
-        <v>-0.9767</v>
-      </c>
-      <c r="R20" t="n">
-        <v>1.7581</v>
-      </c>
       <c r="S20" t="n">
-        <v>-0.518</v>
+        <v>0.185</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.6045</v>
+        <v>0.4327</v>
       </c>
       <c r="U20" t="n">
-        <v>0.08649999999999999</v>
+        <v>-0.2477</v>
       </c>
       <c r="V20" t="n">
-        <v>-1.4959</v>
+        <v>0.6642</v>
       </c>
       <c r="W20" t="n">
         <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>-1.4959</v>
+        <v>0.6642</v>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>play_by_play_2484218_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>J. MARTIN TRENADO</t>
+          <t>S. ROMEO FO</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,73 +2143,78 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-2.6666</v>
+        <v>-0.8218</v>
       </c>
       <c r="E21" t="n">
-        <v>-2.9414</v>
+        <v>-0.9562</v>
       </c>
       <c r="F21" t="n">
-        <v>0.2748</v>
+        <v>0.1344</v>
       </c>
       <c r="G21" t="n">
-        <v>-0.1855</v>
+        <v>-0.4538</v>
       </c>
       <c r="H21" t="n">
-        <v>4.4398</v>
+        <v>-0.5887</v>
       </c>
       <c r="I21" t="n">
-        <v>-4.6253</v>
+        <v>0.1348</v>
       </c>
       <c r="J21" t="n">
-        <v>0.2494</v>
+        <v>-0.6536</v>
       </c>
       <c r="K21" t="n">
-        <v>3.5252</v>
+        <v>-0.6536</v>
       </c>
       <c r="L21" t="n">
-        <v>-3.2757</v>
+        <v>0</v>
       </c>
       <c r="M21" t="n">
-        <v>-0.435</v>
+        <v>0.1998</v>
       </c>
       <c r="N21" t="n">
-        <v>0.9146</v>
+        <v>0.065</v>
       </c>
       <c r="O21" t="n">
-        <v>-1.3496</v>
+        <v>0.1348</v>
       </c>
       <c r="P21" t="n">
-        <v>-2.5395</v>
+        <v>0.3907</v>
       </c>
       <c r="Q21" t="n">
-        <v>-4.2975</v>
+        <v>0</v>
       </c>
       <c r="R21" t="n">
-        <v>1.7581</v>
+        <v>0.3907</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.551</v>
+        <v>-0.4815</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.112</v>
+        <v>-0.3026</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.439</v>
+        <v>-0.1789</v>
       </c>
       <c r="V21" t="n">
-        <v>0.6093</v>
+        <v>-0.2772</v>
       </c>
       <c r="W21" t="n">
-        <v>1.2186</v>
+        <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>-0.6093</v>
+        <v>-0.2772</v>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>play_by_play_2484218_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>M. SEGARRA BAQUES</t>
+          <t>D. ROY CARNICER</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,73 +2226,78 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-2.685</v>
+        <v>-2.3152</v>
       </c>
       <c r="E22" t="n">
-        <v>-3.379</v>
+        <v>-1.8994</v>
       </c>
       <c r="F22" t="n">
-        <v>0.694</v>
+        <v>-0.4158</v>
       </c>
       <c r="G22" t="n">
-        <v>0.5531</v>
+        <v>-1.0828</v>
       </c>
       <c r="H22" t="n">
-        <v>0.4718</v>
+        <v>0.8726</v>
       </c>
       <c r="I22" t="n">
-        <v>0.0813</v>
+        <v>-1.9554</v>
       </c>
       <c r="J22" t="n">
-        <v>-0.2963</v>
+        <v>-0.3182</v>
       </c>
       <c r="K22" t="n">
-        <v>0.431</v>
+        <v>0.2878</v>
       </c>
       <c r="L22" t="n">
-        <v>-0.7274</v>
+        <v>-0.606</v>
       </c>
       <c r="M22" t="n">
-        <v>0.8494</v>
+        <v>-0.7645</v>
       </c>
       <c r="N22" t="n">
-        <v>0.0407</v>
+        <v>0.5848</v>
       </c>
       <c r="O22" t="n">
-        <v>0.8087</v>
+        <v>-1.3494</v>
       </c>
       <c r="P22" t="n">
-        <v>-2.1488</v>
+        <v>0.7814</v>
       </c>
       <c r="Q22" t="n">
-        <v>-3.3208</v>
+        <v>-0.9767</v>
       </c>
       <c r="R22" t="n">
-        <v>1.1721</v>
+        <v>1.7581</v>
       </c>
       <c r="S22" t="n">
-        <v>0.1293</v>
+        <v>-0.518</v>
       </c>
       <c r="T22" t="n">
-        <v>0.2381</v>
+        <v>-0.6045</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.1088</v>
+        <v>0.08649999999999999</v>
       </c>
       <c r="V22" t="n">
-        <v>-1.2186</v>
+        <v>-1.4959</v>
       </c>
       <c r="W22" t="n">
         <v>0</v>
       </c>
       <c r="X22" t="n">
-        <v>-1.2186</v>
+        <v>-1.4959</v>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>play_by_play_2484218_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>--- TOTAL ---</t>
+          <t>J. MARTIN TRENADO</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2203,68 +2309,235 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>10.3675</v>
+        <v>-2.6666</v>
       </c>
       <c r="E23" t="n">
-        <v>4.011900000000001</v>
+        <v>-2.9414</v>
       </c>
       <c r="F23" t="n">
+        <v>0.2748</v>
+      </c>
+      <c r="G23" t="n">
+        <v>-0.1855</v>
+      </c>
+      <c r="H23" t="n">
+        <v>4.4398</v>
+      </c>
+      <c r="I23" t="n">
+        <v>-4.6253</v>
+      </c>
+      <c r="J23" t="n">
+        <v>0.2494</v>
+      </c>
+      <c r="K23" t="n">
+        <v>3.5252</v>
+      </c>
+      <c r="L23" t="n">
+        <v>-3.2757</v>
+      </c>
+      <c r="M23" t="n">
+        <v>-0.435</v>
+      </c>
+      <c r="N23" t="n">
+        <v>0.9146</v>
+      </c>
+      <c r="O23" t="n">
+        <v>-1.3496</v>
+      </c>
+      <c r="P23" t="n">
+        <v>-2.5395</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>-4.2975</v>
+      </c>
+      <c r="R23" t="n">
+        <v>1.7581</v>
+      </c>
+      <c r="S23" t="n">
+        <v>-0.551</v>
+      </c>
+      <c r="T23" t="n">
+        <v>-0.112</v>
+      </c>
+      <c r="U23" t="n">
+        <v>-0.439</v>
+      </c>
+      <c r="V23" t="n">
+        <v>0.6093</v>
+      </c>
+      <c r="W23" t="n">
+        <v>1.2186</v>
+      </c>
+      <c r="X23" t="n">
+        <v>-0.6093</v>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>play_by_play_2484218_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>M. SEGARRA BAQUES</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>TENEA-C.B. ESPARREGUERA</t>
+        </is>
+      </c>
+      <c r="C24" t="n">
+        <v>1</v>
+      </c>
+      <c r="D24" t="n">
+        <v>-2.685</v>
+      </c>
+      <c r="E24" t="n">
+        <v>-3.379</v>
+      </c>
+      <c r="F24" t="n">
+        <v>0.694</v>
+      </c>
+      <c r="G24" t="n">
+        <v>0.5531</v>
+      </c>
+      <c r="H24" t="n">
+        <v>0.4718</v>
+      </c>
+      <c r="I24" t="n">
+        <v>0.0813</v>
+      </c>
+      <c r="J24" t="n">
+        <v>-0.2963</v>
+      </c>
+      <c r="K24" t="n">
+        <v>0.431</v>
+      </c>
+      <c r="L24" t="n">
+        <v>-0.7274</v>
+      </c>
+      <c r="M24" t="n">
+        <v>0.8494</v>
+      </c>
+      <c r="N24" t="n">
+        <v>0.0407</v>
+      </c>
+      <c r="O24" t="n">
+        <v>0.8087</v>
+      </c>
+      <c r="P24" t="n">
+        <v>-2.1488</v>
+      </c>
+      <c r="Q24" t="n">
+        <v>-3.3208</v>
+      </c>
+      <c r="R24" t="n">
+        <v>1.1721</v>
+      </c>
+      <c r="S24" t="n">
+        <v>0.1293</v>
+      </c>
+      <c r="T24" t="n">
+        <v>0.2381</v>
+      </c>
+      <c r="U24" t="n">
+        <v>-0.1088</v>
+      </c>
+      <c r="V24" t="n">
+        <v>-1.2186</v>
+      </c>
+      <c r="W24" t="n">
+        <v>0</v>
+      </c>
+      <c r="X24" t="n">
+        <v>-1.2186</v>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>play_by_play_2484218_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>--- TOTAL ---</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>TENEA-C.B. ESPARREGUERA</t>
+        </is>
+      </c>
+      <c r="C25" t="n">
+        <v>1</v>
+      </c>
+      <c r="D25" t="n">
+        <v>10.3676</v>
+      </c>
+      <c r="E25" t="n">
+        <v>4.011899999999999</v>
+      </c>
+      <c r="F25" t="n">
         <v>6.355600000000001</v>
       </c>
-      <c r="G23" t="n">
+      <c r="G25" t="n">
         <v>12.5315</v>
       </c>
-      <c r="H23" t="n">
+      <c r="H25" t="n">
         <v>17.2501</v>
       </c>
-      <c r="I23" t="n">
+      <c r="I25" t="n">
         <v>-4.7187</v>
       </c>
-      <c r="J23" t="n">
-        <v>13.7802</v>
-      </c>
-      <c r="K23" t="n">
+      <c r="J25" t="n">
+        <v>13.7803</v>
+      </c>
+      <c r="K25" t="n">
         <v>14.4474</v>
       </c>
-      <c r="L23" t="n">
+      <c r="L25" t="n">
         <v>-0.6671999999999996</v>
       </c>
-      <c r="M23" t="n">
+      <c r="M25" t="n">
         <v>-1.2487</v>
       </c>
-      <c r="N23" t="n">
+      <c r="N25" t="n">
         <v>2.8028</v>
       </c>
-      <c r="O23" t="n">
+      <c r="O25" t="n">
         <v>-4.0515</v>
       </c>
-      <c r="P23" t="n">
-        <v>-9.999999999976694e-05</v>
-      </c>
-      <c r="Q23" t="n">
+      <c r="P25" t="n">
+        <v>-0.0001000000000006551</v>
+      </c>
+      <c r="Q25" t="n">
         <v>-12.6972</v>
       </c>
-      <c r="R23" t="n">
+      <c r="R25" t="n">
         <v>12.6973</v>
       </c>
-      <c r="S23" t="n">
+      <c r="S25" t="n">
         <v>-1.555</v>
       </c>
-      <c r="T23" t="n">
+      <c r="T25" t="n">
         <v>-0.4530000000000001</v>
       </c>
-      <c r="U23" t="n">
+      <c r="U25" t="n">
         <v>-1.102</v>
       </c>
-      <c r="V23" t="n">
-        <v>-0.6093</v>
-      </c>
-      <c r="W23" t="n">
+      <c r="V25" t="n">
+        <v>-0.6093000000000002</v>
+      </c>
+      <c r="W25" t="n">
         <v>3.3816</v>
       </c>
-      <c r="X23" t="n">
+      <c r="X25" t="n">
         <v>-3.9908</v>
       </c>
+      <c r="Y25" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
